--- a/data/trans_camb/P6903-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6903-Clase-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 14,04</t>
+          <t>-18,32; 14,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 29,26</t>
+          <t>-6,88; 27,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 26,01</t>
+          <t>-10,0; 26,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 21,23</t>
+          <t>-17,08; 18,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 41,47</t>
+          <t>3,88; 42,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,09; 38,04</t>
+          <t>6,58; 38,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 12,23</t>
+          <t>-12,45; 12,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 30,45</t>
+          <t>3,85; 29,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 28,21</t>
+          <t>4,62; 28,6</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,41; 82,41</t>
+          <t>-58,06; 81,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 170,3</t>
+          <t>-22,89; 156,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,69; 145,05</t>
+          <t>-33,95; 154,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 146,99</t>
+          <t>-55,68; 135,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,1; 280,31</t>
+          <t>6,79; 269,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,4; 269,83</t>
+          <t>15,74; 258,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,67; 67,34</t>
+          <t>-42,82; 69,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,53; 170,59</t>
+          <t>10,56; 158,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 155,66</t>
+          <t>15,1; 159,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 25,45</t>
+          <t>-15,02; 24,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 40,91</t>
+          <t>-4,65; 42,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 17,34</t>
+          <t>-17,58; 20,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,87; 14,62</t>
+          <t>-19,66; 15,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 35,16</t>
+          <t>-2,71; 37,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 26,68</t>
+          <t>-7,67; 26,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 13,01</t>
+          <t>-12,04; 14,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 33,16</t>
+          <t>0,45; 32,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 17,62</t>
+          <t>-7,61; 17,31</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,49; 202,56</t>
+          <t>-50,06; 190,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 293,03</t>
+          <t>-25,46; 321,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,19; 133,53</t>
+          <t>-57,64; 175,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-88,56; 171,08</t>
+          <t>-82,25; 170,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 327,6</t>
+          <t>-16,41; 420,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,48; 293,08</t>
+          <t>-31,62; 317,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,61; 93,5</t>
+          <t>-46,39; 110,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 245,6</t>
+          <t>0,65; 227,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 135,09</t>
+          <t>-28,98; 126,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 1,43</t>
+          <t>-28,28; 0,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 15,65</t>
+          <t>-15,4; 15,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,91; 17,39</t>
+          <t>-19,87; 16,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 35,95</t>
+          <t>-29,91; 34,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 67,41</t>
+          <t>-14,37; 65,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 34,63</t>
+          <t>-28,88; 33,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 4,39</t>
+          <t>-20,75; 4,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 18,94</t>
+          <t>-11,56; 17,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 14,04</t>
+          <t>-16,75; 14,12</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,23; 8,69</t>
+          <t>-66,42; 2,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 55,59</t>
+          <t>-36,65; 52,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,2; 56,88</t>
+          <t>-47,85; 57,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 360,85</t>
+          <t>-56,19; 293,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,09; 609,91</t>
+          <t>-39,79; 659,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 358,66</t>
+          <t>-64,3; 315,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,36; 15,78</t>
+          <t>-50,24; 16,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 61,56</t>
+          <t>-27,46; 57,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-40,77; 44,94</t>
+          <t>-40,62; 45,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 1,45</t>
+          <t>-20,87; 1,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 19,79</t>
+          <t>-2,74; 18,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 15,23</t>
+          <t>-6,81; 16,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 26,17</t>
+          <t>-8,33; 27,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 21,9</t>
+          <t>-9,73; 21,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 21,85</t>
+          <t>-8,32; 21,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 6,76</t>
+          <t>-12,15; 5,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 16,25</t>
+          <t>-2,41; 15,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 13,71</t>
+          <t>-3,18; 14,09</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-55,49; 4,08</t>
+          <t>-56,63; 3,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 71,52</t>
+          <t>-7,62; 66,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 54,33</t>
+          <t>-18,31; 60,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 116,36</t>
+          <t>-22,31; 128,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 103,59</t>
+          <t>-25,0; 93,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 108,71</t>
+          <t>-19,22; 98,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,03; 24,06</t>
+          <t>-33,05; 20,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 55,73</t>
+          <t>-6,4; 54,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 47,06</t>
+          <t>-8,53; 52,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-23,23; 15,37</t>
+          <t>-23,35; 15,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 24,2</t>
+          <t>-12,37; 22,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 25,74</t>
+          <t>-12,42; 24,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-19,99; 19,88</t>
+          <t>-20,87; 20,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 21,55</t>
+          <t>-19,01; 20,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 15,36</t>
+          <t>-32,66; 16,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 11,97</t>
+          <t>-16,39; 13,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 15,75</t>
+          <t>-10,91; 15,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 14,75</t>
+          <t>-21,37; 14,56</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,85; 63,68</t>
+          <t>-54,61; 60,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 93,73</t>
+          <t>-29,02; 92,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-30,98; 101,88</t>
+          <t>-31,8; 92,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 60,22</t>
+          <t>-40,6; 61,92</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 62,3</t>
+          <t>-34,71; 58,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-59,44; 39,87</t>
+          <t>-62,41; 41,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-37,24; 37,41</t>
+          <t>-36,21; 38,71</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 48,01</t>
+          <t>-24,59; 45,5</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 42,56</t>
+          <t>-50,17; 41,01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7,77</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,25</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,76</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,98</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8,54</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,19</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,82; -0,63</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,34; 14,16</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,45; 9,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,52; 13,35</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,41; 20,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,27; 16,88</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,41; 2,44</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,3; 14,52</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,69; 11,03</t>
         </is>
       </c>
     </row>
@@ -1810,47 +1810,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-24,58%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-10,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -1863,282 +1863,65 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-40,49; -2,09</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,02; 49,35</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,54; 33,1</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-15,07; 52,06</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,13; 78,2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,06; 63,74</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-25,2; 8,32</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,69; 49,85</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,28; 38,39</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>-7,77</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>7,25</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3,91</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>10,76</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>7,98</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-3,18</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>8,54</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>5,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>-14,13; -1,34</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>0,2; 14,16</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>-4,73; 10,38</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>-5,4; 12,8</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2,1; 19,88</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-5,51; 16,12</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-8,19; 1,88</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3,17; 14,26</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-1,86; 10,18</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>-24,58%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>22,95%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>12,71%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>34,95%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>25,93%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-10,15%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>27,25%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>16,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>-40,79; -4,91</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 50,01</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>-14,09; 35,78</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>-15,47; 48,02</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>6,26; 78,9</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-13,31; 63,08</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-24,12; 6,57</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>9,51; 50,71</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>-5,31; 35,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A24:A27"/>

--- a/data/trans_camb/P6903-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6903-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,34</t>
+          <t>9,28</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,64</t>
+          <t>22,04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15,87</t>
+          <t>16,13</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 14,11</t>
+          <t>-17,82; 14,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 27,92</t>
+          <t>-5,56; 31,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 26,42</t>
+          <t>-8,49; 27,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,08; 18,33</t>
+          <t>-16,27; 19,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 42,8</t>
+          <t>2,68; 41,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 38,12</t>
+          <t>3,29; 35,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 12,22</t>
+          <t>-11,95; 12,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,85; 29,9</t>
+          <t>3,54; 29,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 28,6</t>
+          <t>3,91; 27,64</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>67,23%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,06; 81,56</t>
+          <t>-57,42; 97,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 156,2</t>
+          <t>-18,38; 186,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,95; 154,8</t>
+          <t>-30,28; 159,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,68; 135,12</t>
+          <t>-52,53; 162,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,79; 269,88</t>
+          <t>8,03; 305,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,74; 258,99</t>
+          <t>4,55; 226,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,82; 69,6</t>
+          <t>-41,72; 64,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 158,72</t>
+          <t>12,13; 164,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,1; 159,1</t>
+          <t>11,0; 155,64</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,4</t>
+          <t>11,53</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,39</t>
+          <t>5,75</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 24,05</t>
+          <t>-14,45; 25,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 42,15</t>
+          <t>-5,49; 40,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 20,31</t>
+          <t>-17,91; 18,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 15,21</t>
+          <t>-21,23; 15,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 37,88</t>
+          <t>-4,05; 37,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 26,9</t>
+          <t>-4,36; 27,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 14,81</t>
+          <t>-12,13; 14,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 32,77</t>
+          <t>2,76; 33,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 17,31</t>
+          <t>-7,48; 18,09</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,06; 190,25</t>
+          <t>-49,09; 201,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 321,18</t>
+          <t>-20,14; 316,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,64; 175,93</t>
+          <t>-57,18; 157,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-82,25; 170,35</t>
+          <t>-83,12; 161,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 420,48</t>
+          <t>-23,18; 382,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 317,78</t>
+          <t>-20,73; 342,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 110,87</t>
+          <t>-47,31; 111,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 227,68</t>
+          <t>6,51; 230,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 126,58</t>
+          <t>-28,69; 136,51</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,97</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,79</t>
+          <t>6,37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,29</t>
+          <t>1,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,28; 0,62</t>
+          <t>-27,89; -0,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 15,24</t>
+          <t>-14,93; 16,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 16,53</t>
+          <t>-16,72; 20,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 34,21</t>
+          <t>-19,64; 39,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 65,85</t>
+          <t>-14,02; 65,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,88; 33,58</t>
+          <t>-25,99; 33,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 4,68</t>
+          <t>-19,96; 5,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 17,16</t>
+          <t>-11,32; 18,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 14,12</t>
+          <t>-13,44; 17,7</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-8,22%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-3,66%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,42; 2,31</t>
+          <t>-64,58; -0,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,65; 52,43</t>
+          <t>-36,06; 58,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,85; 57,02</t>
+          <t>-42,06; 71,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,19; 293,02</t>
+          <t>-47,48; 453,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,79; 659,53</t>
+          <t>-48,39; 578,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,3; 315,62</t>
+          <t>-54,29; 380,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,24; 16,3</t>
+          <t>-48,95; 18,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 57,31</t>
+          <t>-28,23; 64,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-40,62; 45,39</t>
+          <t>-33,61; 63,95</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,47</t>
+          <t>7,97</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,84</t>
+          <t>8,02</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>7,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 1,3</t>
+          <t>-19,45; 1,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 18,73</t>
+          <t>-3,43; 18,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 16,96</t>
+          <t>-3,09; 18,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 27,37</t>
+          <t>-9,06; 27,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 21,62</t>
+          <t>-10,53; 22,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 21,02</t>
+          <t>-9,26; 22,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 5,87</t>
+          <t>-12,29; 6,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 15,19</t>
+          <t>-2,28; 15,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 14,09</t>
+          <t>-1,2; 16,08</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-56,63; 3,97</t>
+          <t>-54,12; 6,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 66,13</t>
+          <t>-8,8; 71,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 60,93</t>
+          <t>-8,07; 65,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 128,75</t>
+          <t>-21,13; 128,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 93,22</t>
+          <t>-26,84; 109,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 98,13</t>
+          <t>-20,74; 106,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-33,05; 20,96</t>
+          <t>-33,79; 25,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 54,11</t>
+          <t>-6,06; 55,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 52,23</t>
+          <t>-4,15; 56,9</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,05</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,36</t>
+          <t>6,58</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>5,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 15,34</t>
+          <t>-21,85; 16,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 22,75</t>
+          <t>-11,76; 21,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 24,7</t>
+          <t>-15,04; 19,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 20,25</t>
+          <t>-22,55; 17,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 20,57</t>
+          <t>-17,74; 18,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 16,26</t>
+          <t>-8,01; 21,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 13,22</t>
+          <t>-16,89; 10,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 15,5</t>
+          <t>-10,35; 15,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 14,56</t>
+          <t>-5,58; 18,06</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-10,05%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-54,61; 60,84</t>
+          <t>-56,18; 68,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 92,82</t>
+          <t>-28,35; 87,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-31,8; 92,79</t>
+          <t>-36,41; 80,14</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-40,6; 61,92</t>
+          <t>-44,87; 48,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 58,6</t>
+          <t>-35,49; 54,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 41,79</t>
+          <t>-14,85; 65,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-36,21; 38,71</t>
+          <t>-37,82; 30,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 45,5</t>
+          <t>-22,49; 45,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 41,01</t>
+          <t>-12,93; 56,56</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>11,55</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>7,68</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-13,82; -0,63</t>
+          <t>-14,03; -1,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,34; 14,16</t>
+          <t>-0,54; 14,48</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 9,63</t>
+          <t>-2,31; 11,95</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 13,35</t>
+          <t>-5,18; 13,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,41; 20,43</t>
+          <t>2,29; 20,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 16,88</t>
+          <t>3,69; 19,31</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 2,44</t>
+          <t>-8,02; 2,76</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,3; 14,52</t>
+          <t>2,87; 14,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 11,03</t>
+          <t>2,99; 13,13</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-40,49; -2,09</t>
+          <t>-41,26; -4,26</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1,02; 49,35</t>
+          <t>-0,78; 51,56</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 33,1</t>
+          <t>-7,2; 43,04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 52,06</t>
+          <t>-14,61; 51,28</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,13; 78,2</t>
+          <t>5,88; 78,05</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 63,74</t>
+          <t>10,58; 75,7</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 8,32</t>
+          <t>-24,26; 10,46</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9,69; 49,85</t>
+          <t>7,59; 49,2</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 38,39</t>
+          <t>8,89; 46,02</t>
         </is>
       </c>
     </row>
